--- a/data/uftm-people.xlsx
+++ b/data/uftm-people.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mestrado Health Professions (2024–2026); Biomedicina (2019–2024)</t>
+          <t>Mestrado Health Professions (2024–2026) | Biomedicina (2019–2024)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
